--- a/output/pdf_financials_xlsx/FPX.xlsx
+++ b/output/pdf_financials_xlsx/FPX.xlsx
@@ -4973,16 +4973,16 @@
         <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>10.493703</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>12.36352</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>12.089004</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>12.427122</v>
       </c>
     </row>
     <row r="93">
@@ -6287,16 +6287,16 @@
         </is>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-6.534463</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-7.069215</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-8.778088</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-9.612992999999999</v>
       </c>
     </row>
     <row r="119">
@@ -8656,7 +8656,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -16390,7 +16394,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -16904,7 +16912,11 @@
           <t>(Decrease) increase in accounts payable related to exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -16978,7 +16990,11 @@
           <t>Increase in accounts receivable related to exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -17430,7 +17446,11 @@
           <t>Increase (decrease) in accounts payable related to exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -17502,7 +17522,11 @@
           <t>Increase (decrease) in accounts receivable related to exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -17882,7 +17906,11 @@
           <t>(Decrease) increase in accounts receivable related to exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FPX.xlsx
+++ b/output/pdf_financials_xlsx/FPX.xlsx
@@ -943,16 +943,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.00711</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000321</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.036488</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.111162</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -975,16 +975,16 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.16176</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>1.234735</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>1.965918</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.851112</v>
       </c>
     </row>
     <row r="13">
@@ -1754,16 +1754,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.814465</v>
+        <v>-0.8215750000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.65285</v>
+        <v>-0.6531709999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.469068</v>
+        <v>-2.505556</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.486543</v>
+        <v>-3.597705</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1786,16 +1786,16 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.711408</v>
+        <v>-3.873168</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-4.44675</v>
+        <v>-5.681485</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.804623</v>
+        <v>-4.770541</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-5.174718</v>
+        <v>-6.02583</v>
       </c>
     </row>
     <row r="28">
@@ -1856,16 +1856,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.814465</v>
+        <v>-0.8215750000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.65285</v>
+        <v>-0.6531709999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.469068</v>
+        <v>-2.505556</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.486543</v>
+        <v>-3.597705</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.623333</v>
+        <v>-3.785093</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-4.307768</v>
+        <v>-5.542503</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.55391</v>
+        <v>-4.519828</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.910761</v>
+        <v>-5.761873</v>
       </c>
     </row>
     <row r="30">
@@ -2098,15 +2098,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.062065</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0.740042</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.740042</v>
@@ -2193,10 +2189,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.105343</v>
+        <v>0.167408</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.379204</v>
+        <v>1.119246</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.119246</v>
@@ -7702,7 +7698,11 @@
           <t>Reclamation deposits 8, 9</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -9398,7 +9398,11 @@
           <t>Reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -9838,7 +9842,11 @@
           <t>Reclamation deposits (note 7)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -13064,7 +13072,11 @@
           <t>Reclamation deposit (note 8) 15,335 6,505</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -14136,7 +14148,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
@@ -14446,7 +14458,11 @@
           <t>Reclamation deposit (note 5)</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -16468,7 +16484,11 @@
           <t>Decrease (increase) in reclamation deposits</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -17222,7 +17242,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -21592,7 +21616,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -27828,7 +27856,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -31132,7 +31160,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E318" s="5" t="n">

--- a/output/pdf_financials_xlsx/FPX.xlsx
+++ b/output/pdf_financials_xlsx/FPX.xlsx
@@ -546,25 +546,17 @@
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>0</v>
@@ -597,25 +589,17 @@
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>0</v>
@@ -648,25 +632,17 @@
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>0</v>
@@ -699,25 +675,17 @@
       <c r="E7" s="3" t="n">
         <v>0.254983</v>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F7" s="3" t="n">
+        <v>0.062473</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.042897</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.056939</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.10715</v>
@@ -750,25 +718,17 @@
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>0.082621</v>
@@ -801,25 +761,17 @@
       <c r="E9" s="3" t="n">
         <v>0.08155999999999999</v>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F9" s="3" t="n">
+        <v>0.07905</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.100265</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>0</v>
@@ -852,25 +804,17 @@
       <c r="E10" s="3" t="n">
         <v>0.336543</v>
       </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F10" s="3" t="n">
+        <v>0.141523</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.130265</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.042897</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.056939</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.189771</v>
@@ -903,25 +847,17 @@
       <c r="E11" s="3" t="n">
         <v>-3.354723</v>
       </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" s="3" t="n">
+        <v>-1.920488</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-1.25076</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>-1.800016</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>-3.972387</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-3.853338</v>
@@ -954,25 +890,17 @@
       <c r="E12" s="3" t="n">
         <v>0.111162</v>
       </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F12" s="3" t="n">
+        <v>0.015711</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.020492</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0.026038</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0.109317</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0.16176</v>
@@ -1005,25 +933,17 @@
       <c r="E13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>-0</v>
@@ -1056,25 +976,17 @@
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>0</v>
@@ -1107,25 +1019,17 @@
       <c r="E15" s="3" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="3" t="n">
+        <v>0.614942</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-0.27166</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>-0.060332</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>-0.007201</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>-0.004838</v>
@@ -1147,10 +1051,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.814465</v>
+        <v>-1.70426</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.65285</v>
+        <v>-1.4542</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-2.469068</v>
@@ -1158,25 +1062,17 @@
       <c r="E16" s="3" t="n">
         <v>-3.486543</v>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F16" s="3" t="n">
+        <v>-1.912048</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-1.24557</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-1.811109</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>-3.838952</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-3.711408</v>
@@ -1198,10 +1094,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.889795</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>0.80135</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1209,25 +1105,17 @@
       <c r="E17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -1394,25 +1282,17 @@
       <c r="E20" s="3" t="n">
         <v>-3.486543</v>
       </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F20" s="3" t="n">
+        <v>-1.912048</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-1.24557</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>-1.811109</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>-3.838952</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-3.711408</v>
@@ -1445,25 +1325,17 @@
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
@@ -1496,25 +1368,17 @@
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>0.075305</v>
@@ -1547,25 +1411,17 @@
       <c r="E23" s="3" t="n">
         <v>-3.486543</v>
       </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F23" s="3" t="n">
+        <v>-1.912048</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-1.24557</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>-1.811109</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>-3.838952</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-3.711408</v>
@@ -1602,25 +1458,17 @@
       <c r="E24" s="3" t="n">
         <v>0.04</v>
       </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F24" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>0.02</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>-0.02</v>
@@ -1657,25 +1505,17 @@
       <c r="E25" s="3" t="n">
         <v>0.04</v>
       </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F25" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>0.02</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>-0.02</v>
@@ -1727,10 +1567,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="3" t="n">
+        <v>-191.9476</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>185.5704</v>
@@ -1754,10 +1592,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.8215750000000001</v>
+        <v>-1.71137</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.6531709999999999</v>
+        <v>-1.454521</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-2.505556</v>
@@ -1765,25 +1603,17 @@
       <c r="E27" s="3" t="n">
         <v>-3.597705</v>
       </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F27" s="3" t="n">
+        <v>-1.927759</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-1.266062</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>-1.837147</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>-3.948269</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-3.873168</v>
@@ -1816,25 +1646,17 @@
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0.088075</v>
@@ -1856,10 +1678,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.8215750000000001</v>
+        <v>-1.71137</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.6531709999999999</v>
+        <v>-1.454521</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-2.505556</v>
@@ -1867,25 +1689,17 @@
       <c r="E29" s="3" t="n">
         <v>-3.597705</v>
       </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F29" s="3" t="n">
+        <v>-1.927759</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-1.266062</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>-1.837147</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>-3.948269</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-3.785093</v>
@@ -1974,10 +1788,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-52.21005010972504</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-55.10590015128594</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -1985,25 +1799,17 @@
       <c r="E31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -3726,25 +3532,23 @@
       <c r="D67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E67" s="3" t="n">
+        <v>0.031569</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.045486</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>0</v>
@@ -5881,7 +5685,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003038</v>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
@@ -5915,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.196385</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -6090,10 +5894,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.317886</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.055837</v>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
@@ -7114,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003038</v>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
@@ -7148,7 +6952,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.196385</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -7167,7 +6971,7 @@
         <v>-0.313959</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.324647</v>
+        <v>-0.327685</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -7201,7 +7005,7 @@
         <v>-3.217222</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1.970122</v>
+        <v>-2.166507</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-1.884165</v>
@@ -7221,7 +7025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P329"/>
+  <dimension ref="A1:P352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17318,7 +17122,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -21080,7 +20888,11 @@
           <t>Future income tax (recovery)</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E184" s="5" t="n">
         <v>-0.07532999999999999</v>
       </c>
@@ -21770,7 +21582,11 @@
           <t>Proceeds from sales of marketable securities</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E193" s="5" t="n">
         <v>0.317886</v>
       </c>
@@ -21844,7 +21660,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -27089,25 +26909,17 @@
       <c r="H263" s="5" t="n">
         <v>0.008022</v>
       </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I263" s="5" t="n">
+        <v>0.012699</v>
+      </c>
+      <c r="J263" s="5" t="n">
+        <v>0.012721</v>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>0.013468</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>0.017367</v>
       </c>
       <c r="M263" s="5" t="n">
         <v>0.026106</v>
@@ -27229,25 +27041,17 @@
       <c r="H265" s="5" t="n">
         <v>0.07391300000000001</v>
       </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I265" s="5" t="n">
+        <v>0.018279</v>
+      </c>
+      <c r="J265" s="5" t="n">
+        <v>0.017279</v>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>0.029429</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>0.039572</v>
       </c>
       <c r="M265" s="5" t="n">
         <v>0.081044</v>
@@ -27587,25 +27391,17 @@
       <c r="H270" s="5" t="n">
         <v>0.043862</v>
       </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I270" s="5" t="n">
+        <v>0.029703</v>
+      </c>
+      <c r="J270" s="5" t="n">
+        <v>0.025875</v>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>0.027767</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>0.101208</v>
       </c>
       <c r="M270" s="5" t="n">
         <v>0.11616</v>
@@ -27657,25 +27453,17 @@
       <c r="H271" s="5" t="n">
         <v>-3.354723</v>
       </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I271" s="5" t="n">
+        <v>-1.920488</v>
+      </c>
+      <c r="J271" s="5" t="n">
+        <v>-1.25076</v>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>-1.800016</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>-3.972387</v>
       </c>
       <c r="M271" s="5" t="n">
         <v>-3.853338</v>
@@ -27875,25 +27663,17 @@
       <c r="H274" s="5" t="n">
         <v>0.111162</v>
       </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I274" s="5" t="n">
+        <v>0.015711</v>
+      </c>
+      <c r="J274" s="5" t="n">
+        <v>0.020492</v>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>0.026038</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>0.109317</v>
       </c>
       <c r="M274" s="5" t="n">
         <v>0.16176</v>
@@ -28013,25 +27793,17 @@
       <c r="H276" s="5" t="n">
         <v>-0.13182</v>
       </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I276" s="5" t="n">
+        <v>0.00844</v>
+      </c>
+      <c r="J276" s="5" t="n">
+        <v>0.00519</v>
+      </c>
+      <c r="K276" s="5" t="n">
+        <v>-0.011093</v>
+      </c>
+      <c r="L276" s="5" t="n">
+        <v>0.133435</v>
       </c>
       <c r="M276" s="5" t="n">
         <v>0.14193</v>
@@ -28320,10 +28092,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L280" s="5" t="n">
+        <v>-3.838952</v>
       </c>
       <c r="M280" s="5" t="n">
         <v>-3.711408</v>
@@ -28817,25 +28587,17 @@
       <c r="H287" s="5" t="n">
         <v>1.022022</v>
       </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I287" s="5" t="n">
+        <v>0.005066</v>
+      </c>
+      <c r="J287" s="5" t="n">
+        <v>0.002914</v>
+      </c>
+      <c r="K287" s="5" t="n">
+        <v>0.001315</v>
+      </c>
+      <c r="L287" s="5" t="n">
+        <v>0.06834899999999999</v>
       </c>
       <c r="M287" s="5" t="n">
         <v>0.360811</v>
@@ -28961,30 +28723,20 @@
       <c r="H289" s="5" t="n">
         <v>0.132432</v>
       </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I289" s="5" t="n">
+        <v>0.019609</v>
+      </c>
+      <c r="J289" s="5" t="n">
+        <v>0.040669</v>
+      </c>
+      <c r="K289" s="5" t="n">
+        <v>0.023219</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>0.116218</v>
+      </c>
+      <c r="M289" s="5" t="n">
+        <v>0.102393</v>
       </c>
       <c r="N289" t="inlineStr">
         <is>
@@ -29015,12 +28767,12 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Depreciation (note 10)</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -29033,11 +28785,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G290" s="5" t="n">
-        <v>0.007872000000000001</v>
-      </c>
-      <c r="H290" s="5" t="n">
-        <v>0.01341</v>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
@@ -29049,20 +28805,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K290" s="5" t="n">
+        <v>0.031997</v>
+      </c>
+      <c r="L290" s="5" t="n">
+        <v>0.05069</v>
+      </c>
+      <c r="M290" s="5" t="n">
+        <v>0.088075</v>
       </c>
       <c r="N290" t="inlineStr">
         <is>
@@ -29093,10 +28843,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Communications</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr"/>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -29107,36 +28861,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G291" s="5" t="n">
-        <v>0.034848</v>
-      </c>
-      <c r="H291" s="5" t="n">
-        <v>0.130885</v>
-      </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I291" s="5" t="n">
+        <v>0.614942</v>
+      </c>
+      <c r="J291" s="5" t="n">
+        <v>-0.27166</v>
+      </c>
+      <c r="K291" s="5" t="n">
+        <v>-0.060332</v>
+      </c>
+      <c r="L291" s="5" t="n">
+        <v>-0.007201</v>
+      </c>
+      <c r="M291" s="5" t="n">
+        <v>0.004838</v>
       </c>
       <c r="N291" t="inlineStr">
         <is>
@@ -29167,12 +28915,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Interest expense (note 10)</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -29185,11 +28933,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G292" s="5" t="n">
-        <v>0.009804999999999999</v>
-      </c>
-      <c r="H292" s="5" t="n">
-        <v>0.008319999999999999</v>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
@@ -29206,15 +28958,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L292" s="5" t="n">
+        <v>0.035372</v>
+      </c>
+      <c r="M292" s="5" t="n">
+        <v>0.014992</v>
       </c>
       <c r="N292" t="inlineStr">
         <is>
@@ -29245,14 +28993,10 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Management fees</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Management fees and salaries (note 13)</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -29263,11 +29007,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G293" s="5" t="n">
-        <v>0.136315</v>
-      </c>
-      <c r="H293" s="5" t="n">
-        <v>0.138701</v>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
@@ -29284,15 +29032,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L293" s="5" t="n">
+        <v>0.734418</v>
+      </c>
+      <c r="M293" s="5" t="n">
+        <v>1.05239</v>
       </c>
       <c r="N293" t="inlineStr">
         <is>
@@ -29323,14 +29067,10 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based compensation (note 11)</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -29341,11 +29081,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G294" s="5" t="n">
-        <v>0.01986</v>
-      </c>
-      <c r="H294" s="5" t="n">
-        <v>0.034347</v>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
@@ -29362,15 +29106,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L294" s="5" t="n">
+        <v>2.276855</v>
+      </c>
+      <c r="M294" s="5" t="n">
+        <v>1.367091</v>
       </c>
       <c r="N294" t="inlineStr">
         <is>
@@ -29401,7 +29141,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Travel, promotion &amp; communication</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -29415,11 +29155,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G295" s="5" t="n">
-        <v>0.910215</v>
-      </c>
-      <c r="H295" s="5" t="n">
-        <v>1.277131</v>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
@@ -29431,20 +29175,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K295" s="5" t="n">
+        <v>0.237094</v>
+      </c>
+      <c r="L295" s="5" t="n">
+        <v>0.539539</v>
+      </c>
+      <c r="M295" s="5" t="n">
+        <v>0.576647</v>
       </c>
       <c r="N295" t="inlineStr">
         <is>
@@ -29470,19 +29208,15 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Travel and promotion</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Gain on settlement of CEBA loan</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -29493,11 +29227,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G296" s="5" t="n">
-        <v>0.027434</v>
-      </c>
-      <c r="H296" s="5" t="n">
-        <v>0.08155999999999999</v>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
@@ -29514,10 +29252,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L296" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
@@ -29548,12 +29284,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Wages and benefits</t>
+          <t>Gain on lease modification</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -29567,11 +29303,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G297" s="5" t="n">
-        <v>0.273067</v>
-      </c>
-      <c r="H297" s="5" t="n">
-        <v>0.390118</v>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
@@ -29588,10 +29328,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L297" s="5" t="n">
+        <v>0.004118</v>
       </c>
       <c r="M297" t="inlineStr">
         <is>
@@ -29627,10 +29365,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Properties/Costs written off</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -29641,11 +29383,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G298" s="5" t="n">
-        <v>-0.674978</v>
-      </c>
-      <c r="H298" s="5" t="n">
-        <v>-0.242982</v>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
@@ -29657,20 +29403,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K298" s="5" t="n">
+        <v>-1.811109</v>
+      </c>
+      <c r="L298" s="5" t="n">
+        <v>-3.838952</v>
+      </c>
+      <c r="M298" s="5" t="n">
+        <v>-3.711408</v>
       </c>
       <c r="N298" t="inlineStr">
         <is>
@@ -29696,19 +29436,15 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Net loss and comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shareholders of FPX Nickel Corp.</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -29719,11 +29455,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G299" s="5" t="n">
-        <v>-2.469068</v>
-      </c>
-      <c r="H299" s="5" t="n">
-        <v>-3.486543</v>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
@@ -29740,15 +29480,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L299" s="5" t="n">
+        <v>-3.838952</v>
+      </c>
+      <c r="M299" s="5" t="n">
+        <v>-3.636103</v>
       </c>
       <c r="N299" t="inlineStr">
         <is>
@@ -29774,15 +29510,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable</t>
+          <t>Net loss and comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable securities</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>Non-controlling interest</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -29793,11 +29533,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G300" s="5" t="n">
-        <v>0.7636039999999999</v>
-      </c>
-      <c r="H300" s="5" t="n">
-        <v>-0.6129599999999999</v>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -29819,10 +29563,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M300" s="5" t="n">
+        <v>0.075305</v>
       </c>
       <c r="N300" t="inlineStr">
         <is>
@@ -29848,17 +29590,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable</t>
+          <t>Net loss and comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
+          <t>Basic and diluted loss per share (note 12) $</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -29871,11 +29613,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G301" s="5" t="n">
-        <v>-1.705464</v>
-      </c>
-      <c r="H301" s="5" t="n">
-        <v>-4.099503</v>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
@@ -29892,15 +29638,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L301" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="M301" s="5" t="n">
+        <v>2e-08</v>
       </c>
       <c r="N301" t="inlineStr">
         <is>
@@ -29926,17 +29668,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable</t>
+          <t>Weighted average number of</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (note 13)</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -29950,35 +29692,25 @@
         </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>3e-08</v>
+        <v>78.798011</v>
       </c>
       <c r="H302" s="5" t="n">
-        <v>4e-08</v>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>88.957381</v>
+      </c>
+      <c r="I302" s="5" t="n">
+        <v>143.503216</v>
+      </c>
+      <c r="J302" s="5" t="n">
+        <v>148.537805</v>
+      </c>
+      <c r="K302" s="5" t="n">
+        <v>165.292927</v>
+      </c>
+      <c r="L302" s="5" t="n">
+        <v>205.820525</v>
+      </c>
+      <c r="M302" s="5" t="n">
+        <v>217.672521</v>
       </c>
       <c r="N302" t="inlineStr">
         <is>
@@ -30004,17 +29736,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Weighted average number of</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Interest expense (notes 10 and 11)</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -30027,11 +29759,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G303" s="5" t="n">
-        <v>78.798011</v>
-      </c>
-      <c r="H303" s="5" t="n">
-        <v>88.957381</v>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
@@ -30043,15 +29779,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K303" s="5" t="n">
+        <v>0.502529</v>
+      </c>
+      <c r="L303" s="5" t="n">
+        <v>0.035372</v>
       </c>
       <c r="M303" t="inlineStr">
         <is>
@@ -30082,20 +29814,24 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Accounting, legal and audit</t>
+          <t>Management fees and salaries (note 14)</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
-      <c r="E304" s="5" t="n">
-        <v>0.018571</v>
-      </c>
-      <c r="F304" s="5" t="n">
-        <v>0.026241</v>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
@@ -30117,15 +29853,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K304" s="5" t="n">
+        <v>0.462443</v>
+      </c>
+      <c r="L304" s="5" t="n">
+        <v>0.734418</v>
       </c>
       <c r="M304" t="inlineStr">
         <is>
@@ -30156,24 +29888,24 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E305" s="5" t="n">
-        <v>0.016928</v>
-      </c>
-      <c r="F305" s="5" t="n">
-        <v>0.015755</v>
+          <t>Share-based compensation (note 12)</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -30195,15 +29927,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K305" s="5" t="n">
+        <v>0.531087</v>
+      </c>
+      <c r="L305" s="5" t="n">
+        <v>2.276855</v>
       </c>
       <c r="M305" t="inlineStr">
         <is>
@@ -30234,20 +29962,24 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Loss on sale of marketable securities</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
-      <c r="E306" s="5" t="n">
-        <v>0.007078</v>
-      </c>
-      <c r="F306" s="5" t="n">
-        <v>0.006572</v>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
@@ -30269,10 +30001,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K306" s="5" t="n">
+        <v>-0.037131</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -30308,24 +30038,28 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Basic and diluted loss per share (note 13)</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E307" s="5" t="n">
-        <v>0.00227</v>
-      </c>
-      <c r="F307" s="5" t="n">
-        <v>0.003265</v>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -30347,15 +30081,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K307" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="L307" s="5" t="n">
+        <v>2e-08</v>
       </c>
       <c r="M307" t="inlineStr">
         <is>
@@ -30386,40 +30116,36 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>General exploration</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
-      <c r="E308" s="5" t="n">
-        <v>0.156584</v>
-      </c>
-      <c r="F308" s="5" t="n">
-        <v>0.170623</v>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G308" s="5" t="n">
+        <v>0.034848</v>
+      </c>
+      <c r="H308" s="5" t="n">
+        <v>0.130885</v>
+      </c>
+      <c r="I308" s="5" t="n">
+        <v>0.022499</v>
+      </c>
+      <c r="J308" s="5" t="n">
+        <v>0.022153</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
@@ -30460,24 +30186,28 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E309" s="5" t="n">
-        <v>0.007771</v>
-      </c>
-      <c r="F309" s="5" t="n">
-        <v>0.007522</v>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -30494,10 +30224,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J309" s="5" t="n">
+        <v>0.032217</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
@@ -30538,24 +30266,28 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Management fees</t>
+          <t>Interest expense (notes 11 and 12)</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E310" s="5" t="n">
-        <v>0.029027</v>
-      </c>
-      <c r="F310" s="5" t="n">
-        <v>0.039543</v>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -30567,15 +30299,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I310" s="5" t="n">
+        <v>0.427821</v>
+      </c>
+      <c r="J310" s="5" t="n">
+        <v>0.471431</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
@@ -30616,24 +30344,24 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Office and administration</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E311" s="5" t="n">
-        <v>0.011036</v>
-      </c>
-      <c r="F311" s="5" t="n">
-        <v>0.010983</v>
+          <t>Management fees and salaries</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -30645,15 +30373,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I311" s="5" t="n">
+        <v>0.238596</v>
+      </c>
+      <c r="J311" s="5" t="n">
+        <v>0.3574</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
@@ -30694,24 +30418,24 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E312" s="5" t="n">
-        <v>0.011513</v>
-      </c>
-      <c r="F312" s="5" t="n">
-        <v>0.01457</v>
+          <t>Property tax and other</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -30728,10 +30452,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J312" s="5" t="n">
+        <v>0.004604</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
@@ -30772,35 +30494,37 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
-      <c r="E313" s="5" t="n">
-        <v>0.012939</v>
-      </c>
-      <c r="F313" s="5" t="n">
-        <v>0.46361</v>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G313" s="5" t="n">
+        <v>0.01986</v>
+      </c>
+      <c r="H313" s="5" t="n">
+        <v>0.034347</v>
+      </c>
+      <c r="I313" s="5" t="n">
+        <v>0.031495</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -30846,24 +30570,24 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Travel and promotion</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E314" s="5" t="n">
-        <v>0.007547</v>
-      </c>
-      <c r="F314" s="5" t="n">
-        <v>0.005062</v>
+          <t>Share-based compensation (note 13)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -30875,15 +30599,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I314" s="5" t="n">
+        <v>0.420729</v>
+      </c>
+      <c r="J314" s="5" t="n">
+        <v>0.434892</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
@@ -30924,40 +30644,40 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Trust and filing fees</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
-      <c r="E315" s="5" t="n">
-        <v>0.019315</v>
-      </c>
-      <c r="F315" s="5" t="n">
-        <v>0.017196</v>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Travel and promotion</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G315" s="5" t="n">
+        <v>0.027434</v>
+      </c>
+      <c r="H315" s="5" t="n">
+        <v>0.08155999999999999</v>
+      </c>
+      <c r="I315" s="5" t="n">
+        <v>0.07905</v>
+      </c>
+      <c r="J315" s="5" t="n">
+        <v>0.100265</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
@@ -30998,20 +30718,24 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Wages and benefits</t>
+          <t>Loss on sale of marketable securities (note 8)</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
-      <c r="E316" s="5" t="n">
-        <v>0.057557</v>
-      </c>
-      <c r="F316" s="5" t="n">
-        <v>0.007036</v>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -31023,15 +30747,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I316" s="5" t="n">
+        <v>-0.007271</v>
+      </c>
+      <c r="J316" s="5" t="n">
+        <v>-0.015302</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
@@ -31072,44 +30792,40 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Net loss before other items</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E317" s="5" t="n">
-        <v>-0.358136</v>
-      </c>
-      <c r="F317" s="5" t="n">
-        <v>-0.787978</v>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="n">
+        <v>-2.469068</v>
+      </c>
+      <c r="H317" s="5" t="n">
+        <v>-3.486543</v>
+      </c>
+      <c r="I317" s="5" t="n">
+        <v>-1.912048</v>
+      </c>
+      <c r="J317" s="5" t="n">
+        <v>-1.24557</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
@@ -31150,44 +30866,36 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Unrealized gain (loss) on marketable</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E318" s="5" t="n">
-        <v>0.00711</v>
-      </c>
-      <c r="F318" s="5" t="n">
-        <v>0.000321</v>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Unrealized gain (loss) on marketable securities</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G318" s="5" t="n">
+        <v>0.7636039999999999</v>
+      </c>
+      <c r="H318" s="5" t="n">
+        <v>-0.6129599999999999</v>
+      </c>
+      <c r="I318" s="5" t="n">
+        <v>-0.015235</v>
+      </c>
+      <c r="J318" s="5" t="n">
+        <v>-0.00779</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
@@ -31228,40 +30936,40 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Unrealized gain (loss) on marketable</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of marketable securities</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
-      <c r="E319" s="5" t="n">
-        <v>0.172923</v>
-      </c>
-      <c r="F319" s="5" t="n">
-        <v>-0.013693</v>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G319" s="5" t="n">
+        <v>-1.705464</v>
+      </c>
+      <c r="H319" s="5" t="n">
+        <v>-4.099503</v>
+      </c>
+      <c r="I319" s="5" t="n">
+        <v>-1.927283</v>
+      </c>
+      <c r="J319" s="5" t="n">
+        <v>-1.25336</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
@@ -31302,42 +31010,40 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Unrealized gain (loss) on marketable</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Loss on disposition of escrow shares</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
-      <c r="E320" s="5" t="n">
-        <v>-0.1738</v>
+          <t>Basic and diluted loss per share (note 13)</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G320" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="H320" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+      <c r="I320" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="J320" s="5" t="n">
+        <v>1e-08</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
@@ -31378,32 +31084,34 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Write-down of mineral properties</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr"/>
-      <c r="E321" s="5" t="n">
-        <v>-0.537892</v>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G321" s="5" t="n">
+        <v>0.007872000000000001</v>
+      </c>
+      <c r="H321" s="5" t="n">
+        <v>0.01341</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
@@ -31454,30 +31162,34 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Other items total</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr"/>
-      <c r="E322" s="5" t="n">
-        <v>-0.531659</v>
-      </c>
-      <c r="F322" s="5" t="n">
-        <v>-0.013372</v>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="n">
+        <v>0.009804999999999999</v>
+      </c>
+      <c r="H322" s="5" t="n">
+        <v>0.008319999999999999</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
@@ -31528,30 +31240,34 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Loss before future income tax recovery</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr"/>
-      <c r="E323" s="5" t="n">
-        <v>-0.889795</v>
-      </c>
-      <c r="F323" s="5" t="n">
-        <v>-0.80135</v>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Management fees</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="n">
+        <v>0.136315</v>
+      </c>
+      <c r="H323" s="5" t="n">
+        <v>0.138701</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
@@ -31602,30 +31318,30 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Future income tax recovery (Note 15)</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
-      <c r="E324" s="5" t="n">
-        <v>0.07532999999999999</v>
-      </c>
-      <c r="F324" s="5" t="n">
-        <v>0.1485</v>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="n">
+        <v>0.910215</v>
+      </c>
+      <c r="H324" s="5" t="n">
+        <v>1.277131</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
@@ -31676,34 +31392,30 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E325" s="5" t="n">
-        <v>-0.814465</v>
-      </c>
-      <c r="F325" s="5" t="n">
-        <v>-0.65285</v>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Wages and benefits</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="n">
+        <v>0.273067</v>
+      </c>
+      <c r="H325" s="5" t="n">
+        <v>0.390118</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
@@ -31754,30 +31466,30 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Deficit – beginning of year</t>
+          <t>Properties/Costs written off</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" s="5" t="n">
-        <v>-9.891347</v>
-      </c>
-      <c r="F326" s="5" t="n">
-        <v>-10.705812</v>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G326" s="5" t="n">
+        <v>-0.674978</v>
+      </c>
+      <c r="H326" s="5" t="n">
+        <v>-0.242982</v>
       </c>
       <c r="I326" t="inlineStr">
         <is>
@@ -31828,20 +31540,20 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Deficit – end of year</t>
+          <t>Accounting, legal and audit</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
       <c r="E327" s="5" t="n">
-        <v>-10.705812</v>
+        <v>0.018571</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>-11.358662</v>
+        <v>0.026241</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
@@ -31902,20 +31614,24 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Loss per share (note 9) $</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E328" s="5" t="n">
-        <v>2e-08</v>
+        <v>0.016928</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.015755</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -31976,71 +31692,1821 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Communications</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" s="5" t="n">
+        <v>0.007078</v>
+      </c>
+      <c r="F329" s="5" t="n">
+        <v>0.006572</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E330" s="5" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="F330" s="5" t="n">
+        <v>0.003265</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>General exploration</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" s="5" t="n">
+        <v>0.156584</v>
+      </c>
+      <c r="F331" s="5" t="n">
+        <v>0.170623</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E332" s="5" t="n">
+        <v>0.007771</v>
+      </c>
+      <c r="F332" s="5" t="n">
+        <v>0.007522</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Management fees</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="n">
+        <v>0.029027</v>
+      </c>
+      <c r="F333" s="5" t="n">
+        <v>0.039543</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Office and administration</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E334" s="5" t="n">
+        <v>0.011036</v>
+      </c>
+      <c r="F334" s="5" t="n">
+        <v>0.010983</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E335" s="5" t="n">
+        <v>0.011513</v>
+      </c>
+      <c r="F335" s="5" t="n">
+        <v>0.01457</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" s="5" t="n">
+        <v>0.012939</v>
+      </c>
+      <c r="F336" s="5" t="n">
+        <v>0.46361</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Travel and promotion</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="n">
+        <v>0.007547</v>
+      </c>
+      <c r="F337" s="5" t="n">
+        <v>0.005062</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Trust and filing fees</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" s="5" t="n">
+        <v>0.019315</v>
+      </c>
+      <c r="F338" s="5" t="n">
+        <v>0.017196</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Wages and benefits</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" s="5" t="n">
+        <v>0.057557</v>
+      </c>
+      <c r="F339" s="5" t="n">
+        <v>0.007036</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Net loss before other items</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E340" s="5" t="n">
+        <v>-0.358136</v>
+      </c>
+      <c r="F340" s="5" t="n">
+        <v>-0.787978</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E341" s="5" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="F341" s="5" t="n">
+        <v>0.000321</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Gain (loss) on sale of marketable securities</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" s="5" t="n">
+        <v>0.172923</v>
+      </c>
+      <c r="F342" s="5" t="n">
+        <v>-0.013693</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Loss on disposition of escrow shares</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" s="5" t="n">
+        <v>-0.1738</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Write-down of mineral properties</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" s="5" t="n">
+        <v>-0.537892</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Other items total</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" s="5" t="n">
+        <v>-0.531659</v>
+      </c>
+      <c r="F345" s="5" t="n">
+        <v>-0.013372</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Loss before future income tax recovery</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E346" s="5" t="n">
+        <v>-0.889795</v>
+      </c>
+      <c r="F346" s="5" t="n">
+        <v>-0.80135</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Future income tax recovery (Note 15)</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="n">
+        <v>0.07532999999999999</v>
+      </c>
+      <c r="F347" s="5" t="n">
+        <v>0.1485</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="n">
+        <v>-0.814465</v>
+      </c>
+      <c r="F348" s="5" t="n">
+        <v>-0.65285</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Deficit – beginning of year</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" s="5" t="n">
+        <v>-9.891347</v>
+      </c>
+      <c r="F349" s="5" t="n">
+        <v>-10.705812</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Deficit – end of year</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" s="5" t="n">
+        <v>-10.705812</v>
+      </c>
+      <c r="F350" s="5" t="n">
+        <v>-11.358662</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Loss per share (note 9) $</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="F351" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
+      <c r="C352" t="inlineStr">
         <is>
           <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
+      <c r="D352" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E329" s="5" t="n">
+      <c r="E352" s="5" t="n">
         <v>54.184228</v>
       </c>
-      <c r="F329" s="5" t="n">
+      <c r="F352" s="5" t="n">
         <v>57.854405</v>
       </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P329" t="inlineStr">
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
         <is>
           <t>-</t>
         </is>
